--- a/data/trans_orig/Q5403-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5403-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2007</t>
+          <t>Población según si es capaz de ir de compras en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23242</t>
+          <t>22922</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>12749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30659</t>
+          <t>30918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>21593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28516</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44010</t>
+          <t>43720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86713</t>
+          <t>86445</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102779</t>
+          <t>102083</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105863</t>
+          <t>105455</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126297</t>
+          <t>126460</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>198815</t>
+          <t>198046</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>224569</t>
+          <t>223710</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15353</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21556</t>
+          <t>23647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31440</t>
+          <t>31982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8575</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22368</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23702</t>
+          <t>23518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45056</t>
+          <t>45242</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35052</t>
+          <t>35433</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>60780</t>
+          <t>61079</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113280</t>
+          <t>112462</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130480</t>
+          <t>130766</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122046</t>
+          <t>122200</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147532</t>
+          <t>147464</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>243449</t>
+          <t>244182</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>273857</t>
+          <t>273942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,37%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19075</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>12343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21166</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>28387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89457</t>
+          <t>89474</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100884</t>
+          <t>100861</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102814</t>
+          <t>103966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121391</t>
+          <t>120830</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199127</t>
+          <t>199544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219902</t>
+          <t>220987</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27351</t>
+          <t>27212</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33038</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43557</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26412</t>
+          <t>27574</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51209</t>
+          <t>50165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>119902</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131295</t>
+          <t>131423</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>146911</t>
+          <t>148197</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>171434</t>
+          <t>171077</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>271654</t>
+          <t>269855</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>299178</t>
+          <t>298587</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13454</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>29372</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72099</t>
+          <t>70741</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60585</t>
+          <t>60298</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93486</t>
+          <t>94026</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30079</t>
+          <t>28795</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53667</t>
+          <t>52318</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77246</t>
+          <t>79436</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>114089</t>
+          <t>113814</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>114138</t>
+          <t>115493</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>158736</t>
+          <t>158559</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>426337</t>
+          <t>426981</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>454418</t>
+          <t>455129</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>502123</t>
+          <t>503019</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>548181</t>
+          <t>548479</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>941049</t>
+          <t>942631</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>993005</t>
+          <t>993334</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2012</t>
+          <t>Población según si es capaz de ir de compras en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>15470</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34707</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23594</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45828</t>
+          <t>44694</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23452</t>
+          <t>24432</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40218</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29370</t>
+          <t>31119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55697</t>
+          <t>57450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105197</t>
+          <t>106138</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>124264</t>
+          <t>124734</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101333</t>
+          <t>101084</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126025</t>
+          <t>125613</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>214511</t>
+          <t>215314</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>246146</t>
+          <t>244907</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>11608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>30986</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>29098</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52456</t>
+          <t>52619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46502</t>
+          <t>47007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75456</t>
+          <t>75517</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27292</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34577</t>
+          <t>35861</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29870</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>54755</t>
+          <t>56782</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105764</t>
+          <t>105354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129213</t>
+          <t>127816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113820</t>
+          <t>112251</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139205</t>
+          <t>140930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>226941</t>
+          <t>223518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>262915</t>
+          <t>261114</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,4%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20047</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20825</t>
+          <t>21384</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41868</t>
+          <t>41468</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29247</t>
+          <t>29177</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55048</t>
+          <t>54701</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17761</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9738</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26249</t>
+          <t>25867</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>18270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38723</t>
+          <t>39964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71902</t>
+          <t>72397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90739</t>
+          <t>90694</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82476</t>
+          <t>81330</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>105705</t>
+          <t>104737</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161384</t>
+          <t>160995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191651</t>
+          <t>191796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>18903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27240</t>
+          <t>28113</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20049</t>
+          <t>20281</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41420</t>
+          <t>41317</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29403</t>
+          <t>28454</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23279</t>
+          <t>23432</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46442</t>
+          <t>44381</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39328</t>
+          <t>38781</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68390</t>
+          <t>67179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>120507</t>
+          <t>121277</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>140816</t>
+          <t>141281</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>178975</t>
+          <t>178572</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>205400</t>
+          <t>204993</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>306194</t>
+          <t>306748</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>339796</t>
+          <t>340446</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38518</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68587</t>
+          <t>66463</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94711</t>
+          <t>94375</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>134913</t>
+          <t>133791</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>140262</t>
+          <t>138858</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>188858</t>
+          <t>189632</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45690</t>
+          <t>45668</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78486</t>
+          <t>78135</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>84623</t>
+          <t>85697</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>122985</t>
+          <t>125859</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137760</t>
+          <t>140707</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>189132</t>
+          <t>189923</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>425811</t>
+          <t>429023</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>467905</t>
+          <t>468177</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>499770</t>
+          <t>500031</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>551107</t>
+          <t>553212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>943890</t>
+          <t>945843</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1008006</t>
+          <t>1008660</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2016</t>
+          <t>Población según si es capaz de ir de compras en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21059</t>
+          <t>21678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26869</t>
+          <t>28954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>21995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42675</t>
+          <t>42999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15312</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>17179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38287</t>
+          <t>36640</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24981</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47470</t>
+          <t>47539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105013</t>
+          <t>105712</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121387</t>
+          <t>121781</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>116293</t>
+          <t>117537</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140145</t>
+          <t>140482</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>229147</t>
+          <t>228556</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>258522</t>
+          <t>257553</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29894</t>
+          <t>29194</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40972</t>
+          <t>41580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25248</t>
+          <t>25034</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49577</t>
+          <t>49675</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36630</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64659</t>
+          <t>66704</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130693</t>
+          <t>131374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148406</t>
+          <t>148115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>148366</t>
+          <t>147016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177883</t>
+          <t>177485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>288770</t>
+          <t>286086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>322551</t>
+          <t>321701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>15357</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30482</t>
+          <t>30650</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19153</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>40871</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>11406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14787</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33560</t>
+          <t>33496</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19465</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>39917</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92785</t>
+          <t>92817</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106578</t>
+          <t>106665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87448</t>
+          <t>85909</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>110477</t>
+          <t>110723</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>185642</t>
+          <t>185080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>213910</t>
+          <t>213524</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,88%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25247</t>
+          <t>25205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33104</t>
+          <t>33146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27882</t>
+          <t>27850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54822</t>
+          <t>54327</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39294</t>
+          <t>39769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>66883</t>
+          <t>68043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>146989</t>
+          <t>146033</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162840</t>
+          <t>162412</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>170959</t>
+          <t>173476</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>201985</t>
+          <t>201927</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>326357</t>
+          <t>325868</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359567</t>
+          <t>358978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29224</t>
+          <t>29026</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50622</t>
+          <t>51283</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51994</t>
+          <t>55252</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90828</t>
+          <t>89855</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90826</t>
+          <t>89562</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134454</t>
+          <t>132515</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31095</t>
+          <t>30382</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>55111</t>
+          <t>54753</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>103662</t>
+          <t>103029</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>146998</t>
+          <t>149657</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>142735</t>
+          <t>141247</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>193742</t>
+          <t>194030</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>494542</t>
+          <t>493153</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>525021</t>
+          <t>525251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>556910</t>
+          <t>553202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>608830</t>
+          <t>606809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1060213</t>
+          <t>1061009</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1123214</t>
+          <t>1122936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,01%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de ir de compras en 2023</t>
+          <t>Población según si es capaz de ir de compras en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>24041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>30782</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45065</t>
+          <t>45087</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45853</t>
+          <t>46271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63726</t>
+          <t>65144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25815</t>
+          <t>25657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25782</t>
+          <t>25178</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39460</t>
+          <t>38354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41639</t>
+          <t>41964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59721</t>
+          <t>60542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104409</t>
+          <t>103750</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120068</t>
+          <t>121096</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101069</t>
+          <t>101068</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117901</t>
+          <t>117843</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>209773</t>
+          <t>209246</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>233803</t>
+          <t>233332</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,3%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15864</t>
+          <t>15719</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>28808</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44436</t>
+          <t>44996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38741</t>
+          <t>38629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57850</t>
+          <t>57125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10968</t>
+          <t>11382</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23353</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48854</t>
+          <t>48649</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47603</t>
+          <t>47640</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>68862</t>
+          <t>67040</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124886</t>
+          <t>124392</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139532</t>
+          <t>139518</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131304</t>
+          <t>131316</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152157</t>
+          <t>150563</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260788</t>
+          <t>261815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286179</t>
+          <t>285981</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,48%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52207</t>
+          <t>51087</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50521</t>
+          <t>49091</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16632</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61094</t>
+          <t>59654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64268</t>
+          <t>64673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111681</t>
+          <t>112054</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125176</t>
+          <t>125199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249938</t>
+          <t>252652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>349473</t>
+          <t>348596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>385229</t>
+          <t>386560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>474880</t>
+          <t>475565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18219</t>
+          <t>17653</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26039</t>
+          <t>26119</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43806</t>
+          <t>42972</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35927</t>
+          <t>36761</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55641</t>
+          <t>57217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11422</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24596</t>
+          <t>23899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35633</t>
+          <t>35573</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53225</t>
+          <t>52994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50701</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72992</t>
+          <t>73609</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164984</t>
+          <t>165976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>180913</t>
+          <t>181451</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>186326</t>
+          <t>185639</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>209027</t>
+          <t>208843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>357247</t>
+          <t>356005</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>385775</t>
+          <t>385994</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,6%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>36958</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56995</t>
+          <t>56763</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71211</t>
+          <t>69445</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166521</t>
+          <t>168497</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113548</t>
+          <t>109247</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>204650</t>
+          <t>205470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52375</t>
+          <t>52236</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76474</t>
+          <t>76092</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>79936</t>
+          <t>79616</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181288</t>
+          <t>181241</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137152</t>
+          <t>134489</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>240065</t>
+          <t>240096</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>523808</t>
+          <t>520923</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>553785</t>
+          <t>551037</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>690602</t>
+          <t>688914</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>883502</t>
+          <t>884748</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1243298</t>
+          <t>1241326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1432776</t>
+          <t>1438997</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5403-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5403-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22922</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12749</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30918</t>
+          <t>30850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21593</t>
+          <t>21599</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11598</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26770</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22939</t>
+          <t>22586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43720</t>
+          <t>43762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86445</t>
+          <t>86145</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102083</t>
+          <t>101808</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>105455</t>
+          <t>106233</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126460</t>
+          <t>126273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>198046</t>
+          <t>197084</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>223710</t>
+          <t>223810</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>22201</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13931</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31982</t>
+          <t>33011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>23141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23518</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45242</t>
+          <t>43612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35433</t>
+          <t>36712</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61079</t>
+          <t>63229</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112462</t>
+          <t>113405</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130766</t>
+          <t>130772</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122200</t>
+          <t>123576</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147464</t>
+          <t>148006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>244182</t>
+          <t>242675</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>273942</t>
+          <t>272781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17218</t>
+          <t>16413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12343</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28387</t>
+          <t>27676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89474</t>
+          <t>90695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100861</t>
+          <t>101520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>103966</t>
+          <t>103120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>120830</t>
+          <t>121028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199544</t>
+          <t>199413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>220987</t>
+          <t>220238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9097</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27212</t>
+          <t>27249</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>13970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32775</t>
+          <t>32214</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21194</t>
+          <t>21090</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41583</t>
+          <t>41837</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27574</t>
+          <t>26824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50165</t>
+          <t>49364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>119902</t>
+          <t>120123</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131423</t>
+          <t>130754</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>148197</t>
+          <t>147519</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>171077</t>
+          <t>172343</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>269855</t>
+          <t>270776</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>298587</t>
+          <t>299268</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>13707</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29372</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41819</t>
+          <t>42509</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>70741</t>
+          <t>73004</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60298</t>
+          <t>58788</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>94026</t>
+          <t>92831</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28795</t>
+          <t>29398</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52318</t>
+          <t>53924</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>79436</t>
+          <t>78046</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113814</t>
+          <t>114321</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>115493</t>
+          <t>112857</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>158559</t>
+          <t>157902</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>426981</t>
+          <t>426991</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>455129</t>
+          <t>454178</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>503019</t>
+          <t>504644</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>548479</t>
+          <t>548216</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>942631</t>
+          <t>941056</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>993334</t>
+          <t>996341</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>16039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15470</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34192</t>
+          <t>34504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23924</t>
+          <t>23012</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44694</t>
+          <t>45238</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24432</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>39395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31119</t>
+          <t>30976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57450</t>
+          <t>56752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106138</t>
+          <t>106603</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>124734</t>
+          <t>124945</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101084</t>
+          <t>102826</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125613</t>
+          <t>127126</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>215314</t>
+          <t>214072</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>244907</t>
+          <t>245463</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11608</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30986</t>
+          <t>29925</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29098</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52619</t>
+          <t>54197</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47007</t>
+          <t>46617</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75517</t>
+          <t>74707</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26847</t>
+          <t>27898</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35861</t>
+          <t>34280</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29712</t>
+          <t>30743</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56782</t>
+          <t>55413</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105354</t>
+          <t>105335</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127816</t>
+          <t>127697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112251</t>
+          <t>113446</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140930</t>
+          <t>139715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>223518</t>
+          <t>227016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>261114</t>
+          <t>261033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,38%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20396</t>
+          <t>19870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21384</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41468</t>
+          <t>40658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29177</t>
+          <t>28591</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>54701</t>
+          <t>53749</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25867</t>
+          <t>26421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18270</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39964</t>
+          <t>37950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72397</t>
+          <t>72235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90694</t>
+          <t>90744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81330</t>
+          <t>82392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104737</t>
+          <t>106206</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160995</t>
+          <t>162317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191796</t>
+          <t>191208</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18903</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28113</t>
+          <t>27388</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20281</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41317</t>
+          <t>40344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>29083</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23432</t>
+          <t>23402</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44381</t>
+          <t>45546</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38781</t>
+          <t>38459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67179</t>
+          <t>66550</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>121277</t>
+          <t>119994</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>141281</t>
+          <t>140953</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>178572</t>
+          <t>178648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204993</t>
+          <t>203593</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>306748</t>
+          <t>307379</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>340446</t>
+          <t>340399</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,97%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37294</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66463</t>
+          <t>67310</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94375</t>
+          <t>92968</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>133791</t>
+          <t>132744</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>138858</t>
+          <t>140410</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>189632</t>
+          <t>188604</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>46133</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78135</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>85697</t>
+          <t>86512</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>125859</t>
+          <t>124358</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140707</t>
+          <t>140090</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>189923</t>
+          <t>190553</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>429023</t>
+          <t>428171</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>468177</t>
+          <t>469295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>500031</t>
+          <t>501349</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>553212</t>
+          <t>552369</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>945843</t>
+          <t>944417</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1008660</t>
+          <t>1006310</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>20998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28954</t>
+          <t>26491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21995</t>
+          <t>21650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42999</t>
+          <t>43645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17179</t>
+          <t>17370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36640</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23895</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47539</t>
+          <t>48242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105712</t>
+          <t>105537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121781</t>
+          <t>122142</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>117537</t>
+          <t>116566</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140482</t>
+          <t>140640</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>228556</t>
+          <t>228762</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257553</t>
+          <t>258188</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41580</t>
+          <t>40768</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22801</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25034</t>
+          <t>24517</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49675</t>
+          <t>48788</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37459</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>66704</t>
+          <t>66215</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>131374</t>
+          <t>130632</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148115</t>
+          <t>147854</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>147016</t>
+          <t>149864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177485</t>
+          <t>178649</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>286086</t>
+          <t>287096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>321701</t>
+          <t>320090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30650</t>
+          <t>30504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>19059</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40871</t>
+          <t>41094</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33496</t>
+          <t>33572</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17149</t>
+          <t>18251</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39917</t>
+          <t>41761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92817</t>
+          <t>92839</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106665</t>
+          <t>107078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85909</t>
+          <t>87346</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>110723</t>
+          <t>111869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>185080</t>
+          <t>185328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>213524</t>
+          <t>213948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,04%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33146</t>
+          <t>32904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20307</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>28806</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54327</t>
+          <t>54144</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39769</t>
+          <t>38649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68043</t>
+          <t>69538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>146033</t>
+          <t>145663</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162412</t>
+          <t>162223</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>173476</t>
+          <t>173019</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>201927</t>
+          <t>202027</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>325868</t>
+          <t>323616</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>358978</t>
+          <t>360236</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29026</t>
+          <t>29997</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51283</t>
+          <t>52359</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55252</t>
+          <t>52682</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89855</t>
+          <t>90772</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89562</t>
+          <t>89065</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>132515</t>
+          <t>131769</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>31087</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54753</t>
+          <t>54726</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>103029</t>
+          <t>102847</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>149657</t>
+          <t>147386</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>141247</t>
+          <t>143491</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>194030</t>
+          <t>192918</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>493153</t>
+          <t>494789</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>525251</t>
+          <t>525322</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>553202</t>
+          <t>552626</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>606809</t>
+          <t>609716</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1061009</t>
+          <t>1064110</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1122936</t>
+          <t>1125038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16898</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24041</t>
+          <t>25381</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37727</t>
+          <t>39988</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30782</t>
+          <t>33581</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45087</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>54624</t>
+          <t>57760</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46271</t>
+          <t>49012</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65144</t>
+          <t>68262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>20257</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25657</t>
+          <t>28565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32083</t>
+          <t>34115</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>27802</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38354</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>50542</t>
+          <t>54372</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>45715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60542</t>
+          <t>64686</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>112727</t>
+          <t>125285</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>103750</t>
+          <t>115237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>121096</t>
+          <t>132930</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>109353</t>
+          <t>116926</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101068</t>
+          <t>107237</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117843</t>
+          <t>125038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>222080</t>
+          <t>242211</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>209246</t>
+          <t>229503</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>233332</t>
+          <t>254689</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>11211</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15719</t>
+          <t>16425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36378</t>
+          <t>39426</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28808</t>
+          <t>31404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44996</t>
+          <t>48171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>47142</t>
+          <t>50637</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38629</t>
+          <t>40905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57125</t>
+          <t>61456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11382</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>27088</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>45595</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33124</t>
+          <t>36741</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48649</t>
+          <t>54525</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>57078</t>
+          <t>64432</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47640</t>
+          <t>53285</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67040</t>
+          <t>77190</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>132684</t>
+          <t>148156</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124392</t>
+          <t>139916</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139518</t>
+          <t>155926</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>141956</t>
+          <t>157019</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131316</t>
+          <t>145227</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150563</t>
+          <t>167965</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>274640</t>
+          <t>305174</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261815</t>
+          <t>291593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>285981</t>
+          <t>320049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>22485</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>16142</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51087</t>
+          <t>30369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>26768</t>
+          <t>29609</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49091</t>
+          <t>39353</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>18352</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23907</t>
+          <t>26244</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59654</t>
+          <t>33385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>34359</t>
+          <t>37745</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>29358</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64673</t>
+          <t>48155</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>119197</t>
+          <t>140229</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112054</t>
+          <t>131695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125199</t>
+          <t>146172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>316026</t>
+          <t>126180</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>252652</t>
+          <t>116705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348596</t>
+          <t>134788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>435223</t>
+          <t>266409</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>386560</t>
+          <t>253956</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475565</t>
+          <t>277720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136094</t>
+          <t>158855</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136094</t>
+          <t>158855</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136094</t>
+          <t>158855</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>496350</t>
+          <t>333764</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>496350</t>
+          <t>333764</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>496350</t>
+          <t>333764</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,22 +9632,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>7636</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17653</t>
+          <t>18438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34174</t>
+          <t>37715</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42972</t>
+          <t>47683</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>45976</t>
+          <t>49839</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36761</t>
+          <t>39508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57217</t>
+          <t>61051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17341</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23899</t>
+          <t>25314</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>43893</t>
+          <t>47970</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35573</t>
+          <t>39378</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52994</t>
+          <t>58303</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>61234</t>
+          <t>65967</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>54917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73609</t>
+          <t>77695</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>174125</t>
+          <t>183141</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>165976</t>
+          <t>175030</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>181451</t>
+          <t>190925</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>197556</t>
+          <t>209681</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>185639</t>
+          <t>196379</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208843</t>
+          <t>222480</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>371682</t>
+          <t>392821</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>356005</t>
+          <t>377080</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>385994</t>
+          <t>406973</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>203268</t>
+          <t>213262</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>203268</t>
+          <t>213262</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>203268</t>
+          <t>213262</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>478892</t>
+          <t>508627</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>478892</t>
+          <t>508627</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>478892</t>
+          <t>508627</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>45908</t>
+          <t>48232</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36958</t>
+          <t>38721</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56763</t>
+          <t>61187</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>128602</t>
+          <t>139614</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69445</t>
+          <t>123176</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>168497</t>
+          <t>156893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>174510</t>
+          <t>187845</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109247</t>
+          <t>169808</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>205470</t>
+          <t>209385</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62917</t>
+          <t>68592</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52236</t>
+          <t>55484</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76092</t>
+          <t>82390</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>140296</t>
+          <t>153924</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>79616</t>
+          <t>138272</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181241</t>
+          <t>170535</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>203214</t>
+          <t>222516</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>134489</t>
+          <t>202224</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>240096</t>
+          <t>244994</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>538733</t>
+          <t>596811</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>520923</t>
+          <t>578628</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>551037</t>
+          <t>611549</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>764891</t>
+          <t>609806</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>688914</t>
+          <t>589714</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>884748</t>
+          <t>628849</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1303624</t>
+          <t>1206617</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1241326</t>
+          <t>1180412</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1438997</t>
+          <t>1233361</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>647559</t>
+          <t>713635</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>647559</t>
+          <t>713635</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>647559</t>
+          <t>713635</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1681348</t>
+          <t>1616978</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1681348</t>
+          <t>1616978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1681348</t>
+          <t>1616978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
